--- a/InputFiles/ICDC/TC29_ICDC_COTC021_Breed-GermnShorthPointer.xlsx
+++ b/InputFiles/ICDC/TC29_ICDC_COTC021_Breed-GermnShorthPointer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epishinavv\git\Commons_Automation\InputFiles\ICDC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/epishinavv/git/Commons_Automation/InputFiles/ICDC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A955795-2A46-4859-B90E-54A72339FD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FE6817-46DE-A84B-AA36-EDF2D4F9F76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
+    <workbookView xWindow="6960" yWindow="780" windowWidth="29040" windowHeight="15720" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
 JOIN 
     df_enrollment enr ON enr."case.case_record_id" = c.case_record_id
 JOIN 
-    df_sample smp ON smp."case.case_record_id" = c.case_record_id
+    df_sample smp ON smp."case.case_id" = c.case_record_id
 LEFT JOIN 
     df_case_file cf ON cf."sample.sample_id" = smp.sample_id
 LEFT JOIN 
@@ -153,7 +153,7 @@
 FROM 
     df_sample smp
 JOIN 
-    df_case c ON smp."case.case_record_id" = c.case_record_id
+    df_case c ON smp."case.case_id" = c.case_record_id
 JOIN 
     df_publication pub ON pub."study.clinical_study_designation" = st.clinical_study_designation
 JOIN 
@@ -174,80 +174,6 @@
    st.clinical_study_designation = 'COTC021' AND dmg.breed = 'German Shorthaired Pointer'
 ORDER BY 
     smp.sample_id ASC
-LIMIT 100;</t>
-  </si>
-  <si>
-    <t>SELECT DISTINCT
-    sf.file_name AS "File Name",
-    sf.file_type AS "File Type",
-    'study' AS "Association",
-    sf.file_description AS "Description",
-    CASE
-        WHEN sf.file_name LIKE '%.bai' THEN 'bai'
-        WHEN sf.file_name LIKE '%.bam' THEN 'bam'
-        WHEN sf.file_name LIKE '%.csv' THEN 'csv'
-        WHEN sf.file_name LIKE '%.doc' THEN 'doc'
-        WHEN sf.file_name LIKE '%.docx' THEN 'docx'
-        WHEN sf.file_name LIKE '%.gz' THEN 'gz'
-        WHEN sf.file_name LIKE '%.pdf' THEN 'pdf'
-        WHEN sf.file_name LIKE '%.rtf' THEN 'rtf'
-        WHEN sf.file_name LIKE '%.tbi' THEN 'tbi'
-        WHEN sf.file_name LIKE '%.tif' THEN 'tif'
-        WHEN sf.file_name LIKE '%.xls' THEN 'xls'
-        WHEN sf.file_name LIKE '%.xlsx' THEN 'xlsx'
-        ELSE 'Unknown'
-    END AS "Format",
-      CASE     
-    WHEN sf.file_size &gt;= 1024 * 1024 * 1024 THEN 
-        CASE 
-            WHEN ROUND(sf.file_size / (1024.0 * 1024.0 * 1024.0), 2) = CAST(ROUND(sf.file_size / (1024.0 * 1024.0 * 1024.0), 0) AS INT) 
-            THEN CAST(CAST(ROUND(sf.file_size / (1024.0 * 1024.0 * 1024.0), 0) AS INT) AS TEXT) || ' GB'
-            ELSE ROUND(sf.file_size / (1024.0 * 1024.0 * 1024.0), 2) || ' GB'
-        END
-    WHEN sf.file_size &gt;= 1024 * 1024 THEN 
-        CASE 
-            WHEN ROUND(sf.file_size / (1024.0 * 1024.0), 2) = CAST(ROUND(sf.file_size / (1024.0 * 1024.0), 0) AS INT) 
-            THEN CAST(CAST(ROUND(sf.file_size / (1024.0 * 1024.0), 0) AS INT) AS TEXT) || ' MB'
-            ELSE ROUND(sf.file_size / (1024.0 * 1024.0), 2) || ' MB'
-        END
-    WHEN sf.file_size &gt;= 1024 THEN 
-        CASE 
-            WHEN ROUND(sf.file_size / 1024.0, 2) = CAST(ROUND(sf.file_size / 1024.0, 0) AS INT) 
-            THEN CAST(CAST(ROUND(sf.file_size / 1024.0, 0) AS INT) AS TEXT) || ' KB'
-            ELSE ROUND(sf.file_size / 1024.0, 2) || ' KB'
-        END
-    ELSE 
-        CASE 
-            WHEN ROUND(sf.file_size, 2) = CAST(ROUND(sf.file_size, 0) AS INT) 
-            THEN CAST(CAST(ROUND(sf.file_size, 0) AS INT) AS TEXT) || ' Bytes'
-            ELSE ROUND(sf.file_size, 2) || ' Bytes'
-        END
-END AS "Size",
-    st.clinical_study_designation AS "Study Code"
-FROM 
-    df_case_file cf
-JOIN 
-    df_sample smp ON cf."sample.sample_id" = smp.sample_id
-JOIN 
-    df_case c ON smp."case.case_record_id" = c.case_record_id
-JOIN 
-    df_study st ON c."study.clinical_study_designation" = st.clinical_study_designation
-JOIN 
-    df_program p ON st."program.program_acronym" = p.program_acronym
-JOIN 
-    df_demographic dmg ON dmg."case.case_record_id" = c.case_record_id
-JOIN 
-    df_diagnosis diag ON diag."case.case_record_id" = c.case_record_id
-JOIN 
-    df_enrollment enr ON enr."case.case_record_id" = c.case_record_id
-JOIN 
-    df_publication pub ON pub."study.clinical_study_designation" = st.clinical_study_designation
-LEFT JOIN 
-    df_study_file sf ON sf."study.clinical_study_designation" = st.clinical_study_designation
-WHERE
-    st.clinical_study_designation = 'COTC021' AND dmg.breed = 'German Shorthaired Pointer'
-ORDER BY 
-    sf.file_name ASC
 LIMIT 100;</t>
   </si>
   <si>
@@ -310,7 +236,7 @@
 JOIN 
     df_sample smp ON cf."sample.sample_id" = smp.sample_id
 JOIN 
-    df_case c ON smp."case.case_record_id" = c.case_record_id
+    df_case c ON smp."case.case_id" = c.case_record_id
 JOIN 
     df_study st ON c."study.clinical_study_designation" = st.clinical_study_designation
 JOIN 
@@ -331,14 +257,95 @@
     cf.file_name ASC
 LIMIT 100;</t>
   </si>
+  <si>
+    <t>SELECT DISTINCT
+    sf.file_name AS "File Name",
+    sf.file_type AS "File Type",
+    'study' AS "Association",
+    sf.file_description AS "Description",
+    CASE
+        WHEN sf.file_name LIKE '%.bai' THEN 'bai'
+        WHEN sf.file_name LIKE '%.bam' THEN 'bam'
+        WHEN sf.file_name LIKE '%.csv' THEN 'csv'
+        WHEN sf.file_name LIKE '%.doc' THEN 'doc'
+        WHEN sf.file_name LIKE '%.docx' THEN 'docx'
+        WHEN sf.file_name LIKE '%.gz' THEN 'gz'
+        WHEN sf.file_name LIKE '%.pdf' THEN 'pdf'
+        WHEN sf.file_name LIKE '%.rtf' THEN 'rtf'
+        WHEN sf.file_name LIKE '%.tbi' THEN 'tbi'
+        WHEN sf.file_name LIKE '%.tif' THEN 'tif'
+        WHEN sf.file_name LIKE '%.xls' THEN 'xls'
+        WHEN sf.file_name LIKE '%.xlsx' THEN 'xlsx'
+        ELSE 'Unknown'
+    END AS "Format",
+      CASE     
+    WHEN sf.file_size &gt;= 1024 * 1024 * 1024 THEN 
+        CASE 
+            WHEN ROUND(sf.file_size / (1024.0 * 1024.0 * 1024.0), 2) = CAST(ROUND(sf.file_size / (1024.0 * 1024.0 * 1024.0), 0) AS INT) 
+            THEN CAST(CAST(ROUND(sf.file_size / (1024.0 * 1024.0 * 1024.0), 0) AS INT) AS TEXT) || ' GB'
+            ELSE ROUND(sf.file_size / (1024.0 * 1024.0 * 1024.0), 2) || ' GB'
+        END
+    WHEN sf.file_size &gt;= 1024 * 1024 THEN 
+        CASE 
+            WHEN ROUND(sf.file_size / (1024.0 * 1024.0), 2) = CAST(ROUND(sf.file_size / (1024.0 * 1024.0), 0) AS INT) 
+            THEN CAST(CAST(ROUND(sf.file_size / (1024.0 * 1024.0), 0) AS INT) AS TEXT) || ' MB'
+            ELSE ROUND(sf.file_size / (1024.0 * 1024.0), 2) || ' MB'
+        END
+    WHEN sf.file_size &gt;= 1024 THEN 
+        CASE 
+            WHEN ROUND(sf.file_size / 1024.0, 2) = CAST(ROUND(sf.file_size / 1024.0, 0) AS INT) 
+            THEN CAST(CAST(ROUND(sf.file_size / 1024.0, 0) AS INT) AS TEXT) || ' KB'
+            ELSE ROUND(sf.file_size / 1024.0, 2) || ' KB'
+        END
+    ELSE 
+        CASE 
+            WHEN ROUND(sf.file_size, 2) = CAST(ROUND(sf.file_size, 0) AS INT) 
+            THEN CAST(CAST(ROUND(sf.file_size, 0) AS INT) AS TEXT) || ' Bytes'
+            ELSE ROUND(sf.file_size, 2) || ' Bytes'
+        END
+END AS "Size",
+    st.clinical_study_designation AS "Study Code"
+FROM 
+    df_case_file cf
+JOIN 
+    df_sample smp ON cf."sample.sample_id" = smp.sample_id
+JOIN 
+    df_case c ON smp."case.case_id" = c.case_record_id
+JOIN 
+    df_study st ON c."study.clinical_study_designation" = st.clinical_study_designation
+JOIN 
+    df_program p ON st."program.program_acronym" = p.program_acronym
+JOIN 
+    df_demographic dmg ON dmg."case.case_record_id" = c.case_record_id
+JOIN 
+    df_diagnosis diag ON diag."case.case_record_id" = c.case_record_id
+JOIN 
+    df_enrollment enr ON enr."case.case_record_id" = c.case_record_id
+JOIN 
+    df_publication pub ON pub."study.clinical_study_designation" = st.clinical_study_designation
+LEFT JOIN 
+    df_study_file sf ON sf."study.clinical_study_designation" = st.clinical_study_designation
+WHERE
+    st.clinical_study_designation = 'COTC021' AND dmg.breed = 'German Shorthaired Pointer'
+ORDER BY 
+    sf.file_name ASC
+LIMIT 100;</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -391,11 +398,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -720,15 +730,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C538400-E87C-4027-A918-A51DB80B3430}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="75.77734375" customWidth="1"/>
-    <col min="4" max="4" width="70.109375" customWidth="1"/>
-    <col min="5" max="5" width="63.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="75.83203125" customWidth="1"/>
+    <col min="4" max="4" width="70.1640625" customWidth="1"/>
+    <col min="5" max="5" width="63.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -745,14 +755,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D2" t="s">
@@ -762,7 +772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -771,29 +781,29 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C6" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
